--- a/python/data/Адапт меро.xlsx
+++ b/python/data/Адапт меро.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nasty\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nasty\PycharmProjects\carbon_ai\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F648B893-BD5F-481A-BAA6-A768031F7169}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86856331-8461-453F-9FA9-8EFC37891FFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8688" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4002,17 +4002,6 @@
     <t>SMHI, Муниципалитеты Остергётланда</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2025-06-16-ovning-i-beredskap-for-framtida-hantering-av-oversvamning</t>
-    </r>
-  </si>
-  <si>
     <t>Риск паводков и подтоплений населённых пунктов</t>
   </si>
   <si>
@@ -4034,9 +4023,6 @@
     <t>Муниципалитет Умео, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2025-03-18-umeas-klimatanpassning---gront-larande-och-medborgardialog-for-en-hallbar-framtid</t>
-  </si>
-  <si>
     <t>Урбанизационные тепловые эффекты и переувлажнение территорий</t>
   </si>
   <si>
@@ -4058,9 +4044,6 @@
     <t>Sametinget, länsstyrelserna Norrbotten, Västerbotten, Jämtland, Västernorrland, Dalarna, Svenska Samernas Riksförbund, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-12-09-klimatanpassning-av-samebyar-genom-samarbete</t>
-  </si>
-  <si>
     <t>Потеря традиционных пастбищ и деградация тундровых экосистем</t>
   </si>
   <si>
@@ -4082,9 +4065,6 @@
     <t>Stadsmiljöförvaltningen, жители города, участвующие художники и архитекторы</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-11-06-regnlekplatsen-i-goteborg---fran-regnig-utmaning-till-lekfull-forebild</t>
-  </si>
-  <si>
     <t>Наводнения и перегрузка ливневых систем</t>
   </si>
   <si>
@@ -4106,17 +4086,6 @@
     <t>Муниципалитет Симришамн, SMHI, местные очистные сооружения</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-05-15-cirkulerat-vatten-minskar-vattenbrist---plattform-framme-for-ateranvant-avloppsvatten</t>
-    </r>
-  </si>
-  <si>
     <t>Дефицит пресной воды и риск засух</t>
   </si>
   <si>
@@ -4135,9 +4104,6 @@
     <t>Hyresbostäder, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-03-26-fastigheter-rustas-for-oversvamningar</t>
-  </si>
-  <si>
     <t>Риск подтоплений жилых территорий и инфраструктуры</t>
   </si>
   <si>
@@ -4159,9 +4125,6 @@
     <t>AB Göta kanalbolag, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-01-17-ab-gota-kanalbolag-integrerar-klimatanpassningsarbetet-i-ordinarie-verksamhet</t>
-  </si>
-  <si>
     <t>Береговая эрозия и разрушение гидротехнических сооружений</t>
   </si>
   <si>
@@ -4183,9 +4146,6 @@
     <t>Муниципалитет Вэрнамо, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-12-11-sa-har-varnamo-minskat-risker-for-oversvamning</t>
-  </si>
-  <si>
     <t>Паводковая опасность и подтопления городской инфраструктуры</t>
   </si>
   <si>
@@ -4204,9 +4164,6 @@
     <t>Город Гётеборг, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-11-27-grona-obligationer-finansierar-klimatanpassning-i-goteborg</t>
-  </si>
-  <si>
     <t>Наводнения и перегрев урбанизированных территорий</t>
   </si>
   <si>
@@ -4228,9 +4185,6 @@
     <t>Skogsstyrelsen, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-09-05-naturnara-skogsbruk-i-tiveden---en-klimatanpassad-forvaltningsfilosofi</t>
-  </si>
-  <si>
     <t>Риск деградации лесных экосистем и пожаров</t>
   </si>
   <si>
@@ -4252,9 +4206,6 @@
     <t>Местные фермерские сообщества, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-08-21-varmare-klimat-oppnar-for-jamtlandskt-hostvete</t>
-  </si>
-  <si>
     <t>Засушливость и нестабильность вегетационного периода</t>
   </si>
   <si>
@@ -4276,9 +4227,6 @@
     <t>Город Солна, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-06-05-kartlaggning-visar-solnas-varmaste-platser---underlag-for-att-klimatanpassa</t>
-  </si>
-  <si>
     <t>Урбанизационный перегрев и дефицит водоудерживающих территорий</t>
   </si>
   <si>
@@ -4300,9 +4248,6 @@
     <t>Шведское агентство по охране природы и SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-04-03-klimatet-och-fjallsakerhet---sa-rustas-lederna</t>
-  </si>
-  <si>
     <t>Разрушение туристической инфраструктуры из-за погодных рисков</t>
   </si>
   <si>
@@ -4324,9 +4269,6 @@
     <t>Шведская церковь, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-01-17-digital-utbildning-for-klimatanpassade-fastigheter</t>
-  </si>
-  <si>
     <t>Уязвимость культурных объектов к экстремальному климату</t>
   </si>
   <si>
@@ -4348,9 +4290,6 @@
     <t>Город Хальмстад, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2022-08-02-sa-sakrades-elen-for-fotbollsarenan-orjans-vall</t>
-  </si>
-  <si>
     <t>Подтопление спортивной инфраструктуры</t>
   </si>
   <si>
@@ -4372,9 +4311,6 @@
     <t>Шведское агентство лесного хозяйства, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2022-03-21-handlingsplan-som-stod-for-klimatanpassning---sa-gjorde-skogsstyrelsen</t>
-  </si>
-  <si>
     <t>Деградация лесных экосистем и угроза пожаров</t>
   </si>
   <si>
@@ -4393,9 +4329,6 @@
     <t>Шведское агентство по защите от чрезвычайных ситуаций, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2022-02-16-okad-brandrisk-i-forandrat-klimat---sa-starks-beredskapen</t>
-  </si>
-  <si>
     <t>Угроза лесным и природным пожарам</t>
   </si>
   <si>
@@ -4414,9 +4347,6 @@
     <t>Компания Castellum, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2021-12-17-bolagets-klimatanalys-vagleder-for-investeringsbeslut</t>
-  </si>
-  <si>
     <t>Уязвимость зданий к климатическим рискам</t>
   </si>
   <si>
@@ -4438,9 +4368,6 @@
     <t>Lundsbrunn Golfklubb, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2021-11-23-golfen-klimatanpassar---lundsbrunn-byggde-bevattningsdamm</t>
-  </si>
-  <si>
     <t>Недостаток воды для газонов и ирригации</t>
   </si>
   <si>
@@ -4462,9 +4389,6 @@
     <t>Region Gotland, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2021-04-12-informationskampanj-forebygger-vattenbrist-pa-gotland</t>
-  </si>
-  <si>
     <t>Дефицит пресной воды и засухи</t>
   </si>
   <si>
@@ -4486,9 +4410,6 @@
     <t>SMHI, länsstyrelsen, муниципалитеты Гётеборгского региона</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2020-06-23-natverk-starker-kommunernas-arbete-med-klimatanpassning</t>
-  </si>
-  <si>
     <t>Низкая адаптивность муниципалитетов к климатическим рискам</t>
   </si>
   <si>
@@ -4510,9 +4431,6 @@
     <t>Город Мальмё, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2018-11-22-tavling-som-metod-for-klimatanpassning</t>
-  </si>
-  <si>
     <t>Наводнения и перегрузка дождевой канализации</t>
   </si>
   <si>
@@ -4528,9 +4446,6 @@
     <t>Среднегодовая температура — 9 °C. Сезонные средние: зима ≈ +1 °C, весна ≈ +9 °C, лето ≈ +19 °C, осень ≈ +11 °C. Безморозный период — 210–220 дней. Годовое количество осадков — 600–700 мм, максимум летом и осенью. Средняя влажность — 75–80 %. Почвы — песчаные, суглинистые, антропогенные. Рельеф — равнинный, 0–50 м над уровнем моря. Климат — морской умеренный. Основные природные риски: ливневые паводки, перегрузка дренажных систем, локальный перегрев.</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2018-11-22-sa-klimatanpassades-en-park-i-malmo</t>
-  </si>
-  <si>
     <t>Наводнения и городские тепловые острова</t>
   </si>
   <si>
@@ -4552,9 +4467,6 @@
     <t>Ферма Hånsta Östgärde, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2018-05-09-alleodling-anpassar-jordbruk-till-forandrat-klimat</t>
-  </si>
-  <si>
     <t>Потери урожая и деградация агроэкосистем</t>
   </si>
   <si>
@@ -4576,9 +4488,6 @@
     <t>Муниципалитет Хальмстад, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2018-04-12-vatmark-oversvamningsskydd-och-rekreation-kombineras-i-getinge</t>
-  </si>
-  <si>
     <t>Наводнения и защита населения</t>
   </si>
   <si>
@@ -4600,17 +4509,6 @@
     <t>Муниципалитет Кристианстад, SMHI</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2017-07-28-okad-beredskap-mot-varmeboljor-i-kristianstad</t>
-    </r>
-  </si>
-  <si>
     <t>Тепловой стресс и риск для здоровья населения</t>
   </si>
   <si>
@@ -4632,17 +4530,6 @@
     <t>Фермер Örjan Svensson, SMHI</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2017-02-14-maskiner-i-lantbruk-anpassas-for-ett-andrat-klimat</t>
-    </r>
-  </si>
-  <si>
     <t>Деградация почв и потери урожая</t>
   </si>
   <si>
@@ -4661,9 +4548,6 @@
     <t>Среднегодовая температура — 7–8 °C. Сезонные средние: зима ≈ 0 °C, весна ≈ +8 °C, лето ≈ +18 °C, осень ≈ +10 °C. Безморозный период — 200–220 дней. Годовое количество осадков — 450–550 мм, максимум летом. Средняя влажность — 70–75 %. Почвы — песчаные и моренные суглинки. Рельеф — равнинный, 0–100 м над уровнем моря. Климат — морской умеренный. Основные природные риски: засухи, дефицит пресной воды, соленение почв.</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2016-11-08-brackvattenverk-for-dricksvatten-pa-gotland</t>
-  </si>
-  <si>
     <t>Дефицит пресной воды</t>
   </si>
   <si>
@@ -4685,9 +4569,6 @@
     <t>Муниципалитет Карлстад, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2016-10-24-skyfallsvag-i-karlstad</t>
-  </si>
-  <si>
     <t>Наводнения и защита городской инфраструктуры</t>
   </si>
   <si>
@@ -4709,9 +4590,6 @@
     <t>Муниципалитет Арвика, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2016-06-28-skyddsvall-mot-oversvamning---kostnad-och-nytta</t>
-  </si>
-  <si>
     <t>Наводнения и защита населённых пунктов</t>
   </si>
   <si>
@@ -4733,9 +4611,6 @@
     <t>SMHI, Visualiseringscenter C</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2015-11-30-klimatvisningar-i-geodomen</t>
-  </si>
-  <si>
     <t>Общественная готовность к климатическим рискам</t>
   </si>
   <si>
@@ -4757,9 +4632,6 @@
     <t>Vilhelmina Model Forest, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2015-10-25-samarbete-for-markanvandning-vilhelmina-model-forest</t>
-  </si>
-  <si>
     <t>Устойчивость лесных и пастбищных экосистем</t>
   </si>
   <si>
@@ -4781,9 +4653,6 @@
     <t>Myndigheten för samhällsskydd och beredskap, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2014-12-12-klosskoping-oversvammas---pedagogiskt-exempel</t>
-  </si>
-  <si>
     <t>Наводнения и образовательная подготовка</t>
   </si>
   <si>
@@ -4805,9 +4674,6 @@
     <t>Владельцы недвижимости, länsantikvarien, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2014-07-09-byggnadsminne-skyddat-mot-ras-och-skred-hoglunda-varmland</t>
-  </si>
-  <si>
     <t>Оползни и разрушение грунтовых оснований</t>
   </si>
   <si>
@@ -4826,17 +4692,6 @@
     <t>Västra strandens reningsverk, SMHI</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-      </rPr>
-      <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2014-07-09-hogflodesrening-pa-vastra-strandens-reningsverk-halmstad</t>
-    </r>
-  </si>
-  <si>
     <t>Наводнения и защита водных ресурсов</t>
   </si>
   <si>
@@ -4858,17 +4713,122 @@
     <t>MKB, муниципалитет Мальмё, SMHI</t>
   </si>
   <si>
-    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2013-10-18-oppen-dagvattenhantering-i-malmostadsdelen-augustenborg</t>
-  </si>
-  <si>
     <t>Наводнения и управление дождевой водой</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2025-06-16-ovning-i-beredskap-for-framtida-hantering-av-oversvamning-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2025-03-18-umeas-klimatanpassning---gront-larande-och-medborgardialog-for-en-hallbar-framtid-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-12-09-klimatanpassning-av-samebyar-genom-samarbete-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-11-06-regnlekplatsen-i-goteborg---fran-regnig-utmaning-till-lekfull-forebild-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-05-15-cirkulerat-vatten-minskar-vattenbrist---plattform-framme-for-ateranvant-avloppsvatten-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-03-26-fastigheter-rustas-for-oversvamningar-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2024-01-17-ab-gota-kanalbolag-integrerar-klimatanpassningsarbetet-i-ordinarie-verksamhet-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-12-11-sa-har-varnamo-minskat-risker-for-oversvamning-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-11-27-grona-obligationer-finansierar-klimatanpassning-i-goteborg-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-09-05-naturnara-skogsbruk-i-tiveden---en-klimatanpassad-forvaltningsfilosofi-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-08-21-varmare-klimat-oppnar-for-jamtlandskt-hostvete-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-06-05-kartlaggning-visar-solnas-varmaste-platser---underlag-for-att-klimatanpassa-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-04-03-klimatet-och-fjallsakerhet---sa-rustas-lederna-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2023-01-17-digital-utbildning-for-klimatanpassade-fastigheter-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2022-08-02-sa-sakrades-elen-for-fotbollsarenan-orjans-vall-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2022-03-21-handlingsplan-som-stod-for-klimatanpassning---sa-gjorde-skogsstyrelsen-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2022-02-16-okad-brandrisk-i-forandrat-klimat---sa-starks-beredskapen-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2021-12-17-bolagets-klimatanalys-vagleder-for-investeringsbeslut-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2021-11-23-golfen-klimatanpassar---lundsbrunn-byggde-bevattningsdamm-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2021-04-12-informationskampanj-forebygger-vattenbrist-pa-gotland-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2020-06-23-natverk-starker-kommunernas-arbete-med-klimatanpassning-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2018-11-22-tavling-som-metod-for-klimatanpassning-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2018-11-22-sa-klimatanpassades-en-park-i-malmo-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2018-05-09-alleodling-anpassar-jordbruk-till-forandrat-klimat-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2018-04-12-vatmark-oversvamningsskydd-och-rekreation-kombineras-i-getinge-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2017-07-28-okad-beredskap-mot-varmeboljor-i-kristianstad-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2017-02-14-maskiner-i-lantbruk-anpassas-for-ett-andrat-klimat-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2016-11-08-brackvattenverk-for-dricksvatten-pa-gotland-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2016-10-24-skyfallsvag-i-karlstad-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2016-06-28-skyddsvall-mot-oversvamning---kostnad-och-nytta-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2015-11-30-klimatvisningar-i-geodomen-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2015-10-25-samarbete-for-markanvandning-vilhelmina-model-forest-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2014-12-12-klosskoping-oversvammas---pedagogiskt-exempel-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2014-07-09-byggnadsminne-skyddat-mot-ras-och-skred-hoglunda-varmland-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2014-07-09-hogflodesrening-pa-vastra-strandens-reningsverk-halmstad-smhi</t>
+  </si>
+  <si>
+    <t>https://klimatanpassning.se/nyheter/nyhetsarkiv/2013-10-18-oppen-dagvattenhantering-i-malmostadsdelen-augustenborg-smhi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4958,6 +4918,15 @@
       <color rgb="FF1155CC"/>
       <name val="Calibri, sans-serif"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -5001,10 +4970,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5054,8 +5024,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -12765,7 +12739,7 @@
     </row>
     <row r="175" spans="1:26">
       <c r="A175" s="6" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>1310</v>
@@ -12785,8 +12759,8 @@
       <c r="G175" s="11" t="s">
         <v>1315</v>
       </c>
-      <c r="H175" s="14" t="s">
-        <v>1316</v>
+      <c r="H175" s="17" t="s">
+        <v>1554</v>
       </c>
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
@@ -12808,28 +12782,28 @@
     </row>
     <row r="176" spans="1:26">
       <c r="A176" s="6" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B176" s="11" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C176" s="11" t="s">
         <v>1318</v>
       </c>
-      <c r="C176" s="11" t="s">
+      <c r="D176" s="11" t="s">
         <v>1319</v>
       </c>
-      <c r="D176" s="11" t="s">
+      <c r="E176" s="11" t="s">
         <v>1320</v>
       </c>
-      <c r="E176" s="11" t="s">
+      <c r="F176" s="6" t="s">
         <v>1321</v>
       </c>
-      <c r="F176" s="6" t="s">
+      <c r="G176" s="11" t="s">
         <v>1322</v>
       </c>
-      <c r="G176" s="11" t="s">
-        <v>1323</v>
-      </c>
-      <c r="H176" s="12" t="s">
-        <v>1324</v>
+      <c r="H176" s="17" t="s">
+        <v>1555</v>
       </c>
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
@@ -12851,28 +12825,28 @@
     </row>
     <row r="177" spans="1:26">
       <c r="A177" s="6" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="B177" s="11" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C177" s="11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D177" s="11" t="s">
         <v>1326</v>
       </c>
-      <c r="C177" s="11" t="s">
+      <c r="E177" s="11" t="s">
         <v>1327</v>
       </c>
-      <c r="D177" s="11" t="s">
+      <c r="F177" s="6" t="s">
         <v>1328</v>
       </c>
-      <c r="E177" s="11" t="s">
+      <c r="G177" s="11" t="s">
         <v>1329</v>
       </c>
-      <c r="F177" s="6" t="s">
-        <v>1330</v>
-      </c>
-      <c r="G177" s="11" t="s">
-        <v>1331</v>
-      </c>
-      <c r="H177" s="12" t="s">
-        <v>1332</v>
+      <c r="H177" s="17" t="s">
+        <v>1556</v>
       </c>
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
@@ -12894,28 +12868,28 @@
     </row>
     <row r="178" spans="1:26">
       <c r="A178" s="6" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="B178" s="11" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C178" s="11" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E178" s="11" t="s">
         <v>1334</v>
       </c>
-      <c r="C178" s="11" t="s">
+      <c r="F178" s="6" t="s">
         <v>1335</v>
       </c>
-      <c r="D178" s="11" t="s">
+      <c r="G178" s="11" t="s">
         <v>1336</v>
       </c>
-      <c r="E178" s="11" t="s">
-        <v>1337</v>
-      </c>
-      <c r="F178" s="6" t="s">
-        <v>1338</v>
-      </c>
-      <c r="G178" s="11" t="s">
-        <v>1339</v>
-      </c>
-      <c r="H178" s="12" t="s">
-        <v>1340</v>
+      <c r="H178" s="17" t="s">
+        <v>1557</v>
       </c>
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
@@ -12937,28 +12911,28 @@
     </row>
     <row r="179" spans="1:26">
       <c r="A179" s="6" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="B179" s="11" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C179" s="11" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E179" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F179" s="6" t="s">
         <v>1342</v>
       </c>
-      <c r="C179" s="11" t="s">
+      <c r="G179" s="11" t="s">
         <v>1343</v>
       </c>
-      <c r="D179" s="11" t="s">
-        <v>1344</v>
-      </c>
-      <c r="E179" s="11" t="s">
-        <v>1345</v>
-      </c>
-      <c r="F179" s="6" t="s">
-        <v>1346</v>
-      </c>
-      <c r="G179" s="11" t="s">
-        <v>1347</v>
-      </c>
-      <c r="H179" s="14" t="s">
-        <v>1348</v>
+      <c r="H179" s="17" t="s">
+        <v>1558</v>
       </c>
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
@@ -12980,28 +12954,28 @@
     </row>
     <row r="180" spans="1:26">
       <c r="A180" s="6" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="E180" s="11" t="s">
         <v>1305</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="G180" s="11" t="s">
-        <v>1354</v>
-      </c>
-      <c r="H180" s="12" t="s">
-        <v>1355</v>
+        <v>1349</v>
+      </c>
+      <c r="H180" s="17" t="s">
+        <v>1559</v>
       </c>
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
@@ -13023,28 +12997,28 @@
     </row>
     <row r="181" spans="1:26">
       <c r="A181" s="6" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="E181" s="11" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
       <c r="G181" s="11" t="s">
-        <v>1362</v>
-      </c>
-      <c r="H181" s="12" t="s">
-        <v>1363</v>
+        <v>1356</v>
+      </c>
+      <c r="H181" s="17" t="s">
+        <v>1560</v>
       </c>
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
@@ -13066,28 +13040,28 @@
     </row>
     <row r="182" spans="1:26">
       <c r="A182" s="6" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="D182" s="11" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="E182" s="11" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="G182" s="11" t="s">
-        <v>1370</v>
-      </c>
-      <c r="H182" s="12" t="s">
-        <v>1371</v>
+        <v>1363</v>
+      </c>
+      <c r="H182" s="17" t="s">
+        <v>1561</v>
       </c>
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
@@ -13109,28 +13083,28 @@
     </row>
     <row r="183" spans="1:26">
       <c r="A183" s="6" t="s">
-        <v>1379</v>
+        <v>1370</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>1373</v>
+        <v>1365</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="E183" s="11" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="G183" s="11" t="s">
-        <v>1377</v>
-      </c>
-      <c r="H183" s="12" t="s">
-        <v>1378</v>
+        <v>1369</v>
+      </c>
+      <c r="H183" s="17" t="s">
+        <v>1562</v>
       </c>
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
@@ -13152,28 +13126,28 @@
     </row>
     <row r="184" spans="1:26">
       <c r="A184" s="6" t="s">
-        <v>1387</v>
+        <v>1377</v>
       </c>
       <c r="B184" s="11" t="s">
-        <v>1380</v>
+        <v>1371</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>1381</v>
+        <v>1372</v>
       </c>
       <c r="D184" s="11" t="s">
-        <v>1382</v>
+        <v>1373</v>
       </c>
       <c r="E184" s="11" t="s">
-        <v>1383</v>
+        <v>1374</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>1384</v>
+        <v>1375</v>
       </c>
       <c r="G184" s="11" t="s">
-        <v>1385</v>
-      </c>
-      <c r="H184" s="12" t="s">
-        <v>1386</v>
+        <v>1376</v>
+      </c>
+      <c r="H184" s="17" t="s">
+        <v>1563</v>
       </c>
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
@@ -13195,28 +13169,28 @@
     </row>
     <row r="185" spans="1:26">
       <c r="A185" s="6" t="s">
-        <v>1395</v>
+        <v>1384</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>1388</v>
+        <v>1378</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>1389</v>
+        <v>1379</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="E185" s="11" t="s">
-        <v>1391</v>
+        <v>1381</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>1392</v>
+        <v>1382</v>
       </c>
       <c r="G185" s="11" t="s">
-        <v>1393</v>
-      </c>
-      <c r="H185" s="12" t="s">
-        <v>1394</v>
+        <v>1383</v>
+      </c>
+      <c r="H185" s="17" t="s">
+        <v>1564</v>
       </c>
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
@@ -13238,28 +13212,28 @@
     </row>
     <row r="186" spans="1:26">
       <c r="A186" s="6" t="s">
-        <v>1403</v>
+        <v>1391</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>1396</v>
+        <v>1385</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>1397</v>
+        <v>1386</v>
       </c>
       <c r="D186" s="11" t="s">
-        <v>1398</v>
+        <v>1387</v>
       </c>
       <c r="E186" s="11" t="s">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>1400</v>
+        <v>1389</v>
       </c>
       <c r="G186" s="11" t="s">
-        <v>1401</v>
-      </c>
-      <c r="H186" s="12" t="s">
-        <v>1402</v>
+        <v>1390</v>
+      </c>
+      <c r="H186" s="17" t="s">
+        <v>1565</v>
       </c>
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
@@ -13281,28 +13255,28 @@
     </row>
     <row r="187" spans="1:26">
       <c r="A187" s="6" t="s">
-        <v>1411</v>
+        <v>1398</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>1404</v>
+        <v>1392</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>1405</v>
+        <v>1393</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>1406</v>
+        <v>1394</v>
       </c>
       <c r="E187" s="11" t="s">
-        <v>1407</v>
+        <v>1395</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>1408</v>
+        <v>1396</v>
       </c>
       <c r="G187" s="11" t="s">
-        <v>1409</v>
-      </c>
-      <c r="H187" s="12" t="s">
-        <v>1410</v>
+        <v>1397</v>
+      </c>
+      <c r="H187" s="17" t="s">
+        <v>1566</v>
       </c>
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
@@ -13324,28 +13298,28 @@
     </row>
     <row r="188" spans="1:26">
       <c r="A188" s="6" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>1412</v>
+        <v>1399</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>1413</v>
+        <v>1400</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>1414</v>
+        <v>1401</v>
       </c>
       <c r="E188" s="11" t="s">
-        <v>1415</v>
+        <v>1402</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>1416</v>
+        <v>1403</v>
       </c>
       <c r="G188" s="11" t="s">
-        <v>1417</v>
-      </c>
-      <c r="H188" s="12" t="s">
-        <v>1418</v>
+        <v>1404</v>
+      </c>
+      <c r="H188" s="17" t="s">
+        <v>1567</v>
       </c>
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
@@ -13367,28 +13341,28 @@
     </row>
     <row r="189" spans="1:26">
       <c r="A189" s="6" t="s">
-        <v>1427</v>
+        <v>1412</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="E189" s="11" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="G189" s="11" t="s">
-        <v>1425</v>
-      </c>
-      <c r="H189" s="12" t="s">
-        <v>1426</v>
+        <v>1411</v>
+      </c>
+      <c r="H189" s="17" t="s">
+        <v>1568</v>
       </c>
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
@@ -13410,28 +13384,28 @@
     </row>
     <row r="190" spans="1:26">
       <c r="A190" s="6" t="s">
-        <v>1435</v>
+        <v>1419</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>1428</v>
+        <v>1413</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>1429</v>
+        <v>1414</v>
       </c>
       <c r="D190" s="11" t="s">
-        <v>1430</v>
+        <v>1415</v>
       </c>
       <c r="E190" s="11" t="s">
-        <v>1431</v>
+        <v>1416</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>1432</v>
+        <v>1417</v>
       </c>
       <c r="G190" s="11" t="s">
-        <v>1433</v>
-      </c>
-      <c r="H190" s="12" t="s">
-        <v>1434</v>
+        <v>1418</v>
+      </c>
+      <c r="H190" s="17" t="s">
+        <v>1569</v>
       </c>
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
@@ -13453,28 +13427,28 @@
     </row>
     <row r="191" spans="1:26">
       <c r="A191" s="6" t="s">
-        <v>1442</v>
+        <v>1425</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>1436</v>
+        <v>1420</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>1437</v>
+        <v>1421</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>1438</v>
+        <v>1422</v>
       </c>
       <c r="E191" s="11" t="s">
-        <v>1431</v>
+        <v>1416</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>1439</v>
+        <v>1423</v>
       </c>
       <c r="G191" s="11" t="s">
-        <v>1440</v>
-      </c>
-      <c r="H191" s="12" t="s">
-        <v>1441</v>
+        <v>1424</v>
+      </c>
+      <c r="H191" s="17" t="s">
+        <v>1570</v>
       </c>
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
@@ -13496,28 +13470,28 @@
     </row>
     <row r="192" spans="1:26">
       <c r="A192" s="6" t="s">
-        <v>1449</v>
+        <v>1431</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>1443</v>
+        <v>1426</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>1444</v>
+        <v>1427</v>
       </c>
       <c r="D192" s="11" t="s">
-        <v>1445</v>
+        <v>1428</v>
       </c>
       <c r="E192" s="11" t="s">
-        <v>1431</v>
+        <v>1416</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>1446</v>
+        <v>1429</v>
       </c>
       <c r="G192" s="11" t="s">
-        <v>1447</v>
-      </c>
-      <c r="H192" s="12" t="s">
-        <v>1448</v>
+        <v>1430</v>
+      </c>
+      <c r="H192" s="17" t="s">
+        <v>1571</v>
       </c>
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
@@ -13539,28 +13513,28 @@
     </row>
     <row r="193" spans="1:26">
       <c r="A193" s="6" t="s">
-        <v>1457</v>
+        <v>1438</v>
       </c>
       <c r="B193" s="11" t="s">
-        <v>1450</v>
+        <v>1432</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>1451</v>
+        <v>1433</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>1452</v>
+        <v>1434</v>
       </c>
       <c r="E193" s="11" t="s">
-        <v>1453</v>
+        <v>1435</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>1454</v>
+        <v>1436</v>
       </c>
       <c r="G193" s="11" t="s">
-        <v>1455</v>
-      </c>
-      <c r="H193" s="12" t="s">
-        <v>1456</v>
+        <v>1437</v>
+      </c>
+      <c r="H193" s="17" t="s">
+        <v>1572</v>
       </c>
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
@@ -13582,28 +13556,28 @@
     </row>
     <row r="194" spans="1:26">
       <c r="A194" s="6" t="s">
-        <v>1465</v>
+        <v>1445</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>1458</v>
+        <v>1439</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>1459</v>
+        <v>1440</v>
       </c>
       <c r="D194" s="11" t="s">
-        <v>1460</v>
+        <v>1441</v>
       </c>
       <c r="E194" s="11" t="s">
-        <v>1461</v>
+        <v>1442</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>1462</v>
+        <v>1443</v>
       </c>
       <c r="G194" s="11" t="s">
-        <v>1463</v>
-      </c>
-      <c r="H194" s="12" t="s">
-        <v>1464</v>
+        <v>1444</v>
+      </c>
+      <c r="H194" s="17" t="s">
+        <v>1573</v>
       </c>
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
@@ -13625,28 +13599,28 @@
     </row>
     <row r="195" spans="1:26">
       <c r="A195" s="6" t="s">
-        <v>1473</v>
+        <v>1452</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>1466</v>
+        <v>1446</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>1467</v>
+        <v>1447</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>1468</v>
+        <v>1448</v>
       </c>
       <c r="E195" s="11" t="s">
-        <v>1469</v>
+        <v>1449</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>1470</v>
+        <v>1450</v>
       </c>
       <c r="G195" s="11" t="s">
-        <v>1471</v>
-      </c>
-      <c r="H195" s="12" t="s">
-        <v>1472</v>
+        <v>1451</v>
+      </c>
+      <c r="H195" s="17" t="s">
+        <v>1574</v>
       </c>
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
@@ -13668,28 +13642,28 @@
     </row>
     <row r="196" spans="1:26">
       <c r="A196" s="6" t="s">
-        <v>1481</v>
+        <v>1459</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>1474</v>
+        <v>1453</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>1475</v>
+        <v>1454</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>1476</v>
+        <v>1455</v>
       </c>
       <c r="E196" s="11" t="s">
-        <v>1477</v>
+        <v>1456</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>1478</v>
+        <v>1457</v>
       </c>
       <c r="G196" s="11" t="s">
-        <v>1479</v>
-      </c>
-      <c r="H196" s="12" t="s">
-        <v>1480</v>
+        <v>1458</v>
+      </c>
+      <c r="H196" s="17" t="s">
+        <v>1575</v>
       </c>
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
@@ -13711,28 +13685,28 @@
     </row>
     <row r="197" spans="1:26">
       <c r="A197" s="6" t="s">
-        <v>1487</v>
+        <v>1464</v>
       </c>
       <c r="B197" s="11" t="s">
-        <v>1482</v>
+        <v>1460</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>1483</v>
+        <v>1461</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>1484</v>
+        <v>1462</v>
       </c>
       <c r="E197" s="11" t="s">
-        <v>1477</v>
+        <v>1456</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>1485</v>
+        <v>1463</v>
       </c>
       <c r="G197" s="11" t="s">
-        <v>1479</v>
-      </c>
-      <c r="H197" s="12" t="s">
-        <v>1486</v>
+        <v>1458</v>
+      </c>
+      <c r="H197" s="17" t="s">
+        <v>1576</v>
       </c>
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
@@ -13754,28 +13728,28 @@
     </row>
     <row r="198" spans="1:26">
       <c r="A198" s="6" t="s">
-        <v>1495</v>
+        <v>1471</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>1488</v>
+        <v>1465</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>1489</v>
+        <v>1466</v>
       </c>
       <c r="D198" s="11" t="s">
-        <v>1490</v>
+        <v>1467</v>
       </c>
       <c r="E198" s="11" t="s">
-        <v>1491</v>
+        <v>1468</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>1492</v>
+        <v>1469</v>
       </c>
       <c r="G198" s="11" t="s">
-        <v>1493</v>
-      </c>
-      <c r="H198" s="12" t="s">
-        <v>1494</v>
+        <v>1470</v>
+      </c>
+      <c r="H198" s="17" t="s">
+        <v>1577</v>
       </c>
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
@@ -13797,28 +13771,28 @@
     </row>
     <row r="199" spans="1:26">
       <c r="A199" s="6" t="s">
-        <v>1503</v>
+        <v>1478</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>1496</v>
+        <v>1472</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>1497</v>
+        <v>1473</v>
       </c>
       <c r="D199" s="11" t="s">
-        <v>1498</v>
+        <v>1474</v>
       </c>
       <c r="E199" s="11" t="s">
-        <v>1499</v>
+        <v>1475</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>1500</v>
+        <v>1476</v>
       </c>
       <c r="G199" s="11" t="s">
-        <v>1501</v>
-      </c>
-      <c r="H199" s="12" t="s">
-        <v>1502</v>
+        <v>1477</v>
+      </c>
+      <c r="H199" s="17" t="s">
+        <v>1578</v>
       </c>
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
@@ -13840,28 +13814,28 @@
     </row>
     <row r="200" spans="1:26">
       <c r="A200" s="6" t="s">
-        <v>1511</v>
+        <v>1485</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>1504</v>
+        <v>1479</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>1505</v>
+        <v>1480</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>1506</v>
+        <v>1481</v>
       </c>
       <c r="E200" s="11" t="s">
-        <v>1507</v>
+        <v>1482</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>1508</v>
+        <v>1483</v>
       </c>
       <c r="G200" s="11" t="s">
-        <v>1509</v>
-      </c>
-      <c r="H200" s="14" t="s">
-        <v>1510</v>
+        <v>1484</v>
+      </c>
+      <c r="H200" s="17" t="s">
+        <v>1579</v>
       </c>
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
@@ -13883,28 +13857,28 @@
     </row>
     <row r="201" spans="1:26">
       <c r="A201" s="6" t="s">
-        <v>1519</v>
+        <v>1492</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>1512</v>
+        <v>1486</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>1513</v>
+        <v>1487</v>
       </c>
       <c r="D201" s="11" t="s">
-        <v>1514</v>
+        <v>1488</v>
       </c>
       <c r="E201" s="11" t="s">
-        <v>1515</v>
+        <v>1489</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>1516</v>
+        <v>1490</v>
       </c>
       <c r="G201" s="11" t="s">
-        <v>1517</v>
-      </c>
-      <c r="H201" s="14" t="s">
-        <v>1518</v>
+        <v>1491</v>
+      </c>
+      <c r="H201" s="17" t="s">
+        <v>1580</v>
       </c>
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
@@ -13926,28 +13900,28 @@
     </row>
     <row r="202" spans="1:26">
       <c r="A202" s="6" t="s">
-        <v>1526</v>
+        <v>1498</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>1520</v>
+        <v>1493</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>1521</v>
+        <v>1494</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>1522</v>
+        <v>1495</v>
       </c>
       <c r="E202" s="11" t="s">
-        <v>1523</v>
+        <v>1496</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>1524</v>
+        <v>1497</v>
       </c>
       <c r="G202" s="11" t="s">
-        <v>1463</v>
-      </c>
-      <c r="H202" s="12" t="s">
-        <v>1525</v>
+        <v>1444</v>
+      </c>
+      <c r="H202" s="17" t="s">
+        <v>1581</v>
       </c>
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
@@ -13969,28 +13943,28 @@
     </row>
     <row r="203" spans="1:26">
       <c r="A203" s="6" t="s">
-        <v>1534</v>
+        <v>1505</v>
       </c>
       <c r="B203" s="11" t="s">
-        <v>1527</v>
+        <v>1499</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>1528</v>
+        <v>1500</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>1529</v>
+        <v>1501</v>
       </c>
       <c r="E203" s="11" t="s">
-        <v>1530</v>
+        <v>1502</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>1531</v>
+        <v>1503</v>
       </c>
       <c r="G203" s="11" t="s">
-        <v>1532</v>
-      </c>
-      <c r="H203" s="12" t="s">
-        <v>1533</v>
+        <v>1504</v>
+      </c>
+      <c r="H203" s="17" t="s">
+        <v>1582</v>
       </c>
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
@@ -14012,28 +13986,28 @@
     </row>
     <row r="204" spans="1:26">
       <c r="A204" s="6" t="s">
-        <v>1542</v>
+        <v>1512</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>1535</v>
+        <v>1506</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>1536</v>
+        <v>1507</v>
       </c>
       <c r="D204" s="11" t="s">
-        <v>1537</v>
+        <v>1508</v>
       </c>
       <c r="E204" s="11" t="s">
-        <v>1538</v>
+        <v>1509</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>1539</v>
+        <v>1510</v>
       </c>
       <c r="G204" s="11" t="s">
-        <v>1540</v>
-      </c>
-      <c r="H204" s="12" t="s">
-        <v>1541</v>
+        <v>1511</v>
+      </c>
+      <c r="H204" s="17" t="s">
+        <v>1583</v>
       </c>
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
@@ -14055,28 +14029,28 @@
     </row>
     <row r="205" spans="1:26">
       <c r="A205" s="6" t="s">
-        <v>1550</v>
+        <v>1519</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>1543</v>
+        <v>1513</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>1544</v>
+        <v>1514</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>1545</v>
+        <v>1515</v>
       </c>
       <c r="E205" s="11" t="s">
-        <v>1546</v>
+        <v>1516</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>1547</v>
+        <v>1517</v>
       </c>
       <c r="G205" s="11" t="s">
-        <v>1548</v>
-      </c>
-      <c r="H205" s="12" t="s">
-        <v>1549</v>
+        <v>1518</v>
+      </c>
+      <c r="H205" s="17" t="s">
+        <v>1584</v>
       </c>
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
@@ -14098,28 +14072,28 @@
     </row>
     <row r="206" spans="1:26">
       <c r="A206" s="6" t="s">
-        <v>1558</v>
+        <v>1526</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>1551</v>
+        <v>1520</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>1552</v>
+        <v>1521</v>
       </c>
       <c r="D206" s="11" t="s">
-        <v>1553</v>
+        <v>1522</v>
       </c>
       <c r="E206" s="11" t="s">
-        <v>1554</v>
+        <v>1523</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>1555</v>
+        <v>1524</v>
       </c>
       <c r="G206" s="11" t="s">
-        <v>1556</v>
-      </c>
-      <c r="H206" s="12" t="s">
-        <v>1557</v>
+        <v>1525</v>
+      </c>
+      <c r="H206" s="17" t="s">
+        <v>1585</v>
       </c>
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
@@ -14141,28 +14115,28 @@
     </row>
     <row r="207" spans="1:26">
       <c r="A207" s="6" t="s">
-        <v>1566</v>
+        <v>1533</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>1559</v>
+        <v>1527</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>1560</v>
+        <v>1528</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>1561</v>
+        <v>1529</v>
       </c>
       <c r="E207" s="11" t="s">
-        <v>1562</v>
+        <v>1530</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>1563</v>
+        <v>1531</v>
       </c>
       <c r="G207" s="11" t="s">
-        <v>1564</v>
-      </c>
-      <c r="H207" s="12" t="s">
-        <v>1565</v>
+        <v>1532</v>
+      </c>
+      <c r="H207" s="17" t="s">
+        <v>1586</v>
       </c>
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
@@ -14184,28 +14158,28 @@
     </row>
     <row r="208" spans="1:26">
       <c r="A208" s="6" t="s">
-        <v>1574</v>
+        <v>1540</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>1567</v>
+        <v>1534</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>1568</v>
+        <v>1535</v>
       </c>
       <c r="D208" s="11" t="s">
-        <v>1569</v>
+        <v>1536</v>
       </c>
       <c r="E208" s="11" t="s">
-        <v>1570</v>
+        <v>1537</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>1571</v>
+        <v>1538</v>
       </c>
       <c r="G208" s="11" t="s">
-        <v>1572</v>
-      </c>
-      <c r="H208" s="12" t="s">
-        <v>1573</v>
+        <v>1539</v>
+      </c>
+      <c r="H208" s="17" t="s">
+        <v>1587</v>
       </c>
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
@@ -14227,28 +14201,28 @@
     </row>
     <row r="209" spans="1:26">
       <c r="A209" s="6" t="s">
-        <v>1581</v>
+        <v>1546</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>1575</v>
+        <v>1541</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>1576</v>
+        <v>1542</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>1577</v>
+        <v>1543</v>
       </c>
       <c r="E209" s="11" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>1578</v>
+        <v>1544</v>
       </c>
       <c r="G209" s="11" t="s">
-        <v>1579</v>
-      </c>
-      <c r="H209" s="14" t="s">
-        <v>1580</v>
+        <v>1545</v>
+      </c>
+      <c r="H209" s="17" t="s">
+        <v>1588</v>
       </c>
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
@@ -14270,28 +14244,28 @@
     </row>
     <row r="210" spans="1:26">
       <c r="A210" s="6" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B210" s="11" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C210" s="11" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D210" s="11" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E210" s="11" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G210" s="11" t="s">
+        <v>1552</v>
+      </c>
+      <c r="H210" s="17" t="s">
         <v>1589</v>
-      </c>
-      <c r="B210" s="11" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C210" s="11" t="s">
-        <v>1583</v>
-      </c>
-      <c r="D210" s="11" t="s">
-        <v>1584</v>
-      </c>
-      <c r="E210" s="11" t="s">
-        <v>1585</v>
-      </c>
-      <c r="F210" s="6" t="s">
-        <v>1586</v>
-      </c>
-      <c r="G210" s="11" t="s">
-        <v>1587</v>
-      </c>
-      <c r="H210" s="12" t="s">
-        <v>1588</v>
       </c>
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
